--- a/documentos/Propuesta de investigacion y estructura de datos.xlsx
+++ b/documentos/Propuesta de investigacion y estructura de datos.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja1'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja1'!$A$3:$G$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,9 +20,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.#"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,15 +34,21 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001A1A1A"/>
+      <color rgb="001F2933"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -51,12 +57,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001B3A4B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E3F0"/>
+        <fgColor rgb="00E7F0F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,7 +76,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -73,39 +84,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
     <border>
       <left style="thin">
-        <color rgb="00B0B8C4"/>
+        <color rgb="00D5DEE7"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B8C4"/>
+        <color rgb="00D5DEE7"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B8C4"/>
+        <color rgb="00D5DEE7"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B8C4"/>
+        <color rgb="00D5DEE7"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -470,13 +486,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -485,391 +502,401 @@
     <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Propuesta de investigación y estructura de datos</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="10" customHeight="1"/>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Edad</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Usa Redes Sociales</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Red Principal</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Horas al Día</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Situación Económica</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Ahorro de Emergencia</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SE001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B4" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>SE002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B5" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E5" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SE003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B6" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SE004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B7" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SE005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B8" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>SE006</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B9" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SE007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B10" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>SE008</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B11" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E11" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SE009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B12" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E12" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>SE010</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B13" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A3:G13"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="3" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CHoja1</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008FA8BF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/documentos/Propuesta de investigacion y estructura de datos.xlsx
+++ b/documentos/Propuesta de investigacion y estructura de datos.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja1'!$A$3:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja1'!$A$2:$G$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.#"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,7 +35,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -44,11 +45,29 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001F2933"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="008FA8BF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00A93226"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005C6B7A"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,17 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B3A4B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7F0F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,8 +84,13 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -84,46 +98,53 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
     <border>
       <left style="thin">
-        <color rgb="00D5DEE7"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="00D5DEE7"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="00D5DEE7"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D5DEE7"/>
+        <color rgb="00000000"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,10 +511,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -502,7 +523,7 @@
     <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Propuesta de investigación y estructura de datos</t>
@@ -515,380 +536,379 @@
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
     </row>
-    <row r="2" ht="10" customHeight="1"/>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Edad</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Usa Redes Sociales</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Red Principal</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Horas al Día</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Situación Económica</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Ahorro de Emergencia</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>SE001</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B3" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>SE002</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B4" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E4" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SE003</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>SE004</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B6" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SE005</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E7" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>SE006</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B8" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SE007</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>SE008</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B10" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E10" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SE009</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E11" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>SE010</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B12" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G13"/>
+  <autoFilter ref="A2:G12"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageMargins left="0.45" right="0.45" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="3" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -902,7 +922,204 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Hoja2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C65911"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Propuesta de investigación y estructura de datos (Hoja3)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Edad</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Usa Redes Sociales</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Red Principal</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Horas al Día</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Situación Económica</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Ahorro de Emergencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SE003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Edad</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Usa Redes Sociales</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Red Principal</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Horas al Día</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Situación Económica</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Ahorro de Emergencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>PE004</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Problemas Económicos</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>PE004 es el caso distinto: más horas en TikTok, problemas económicos y sin ahorro de emergencia.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <pageMargins left="0.45" right="0.45" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="3" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>